--- a/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseApplication.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseApplication.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="采购申请单数据" sheetId="1" r:id="rId1"/>
@@ -27,11 +27,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>申请单号</t>
   </si>
   <si>
+    <t>来源单号</t>
+  </si>
+  <si>
     <t>单据状态</t>
   </si>
   <si>
@@ -90,6 +93,9 @@
   </si>
   <si>
     <t>{.code}</t>
+  </si>
+  <si>
+    <t>{.sourceCode}</t>
   </si>
   <si>
     <t>{.approveStatusName}</t>
@@ -655,7 +661,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1346,10 +1352,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <cols>
+    <col min="2" max="2" width="11.125" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="45" spans="1:20">
+    <row r="1" ht="45" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1410,67 +1420,73 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:21">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseApplication.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseApplication.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="采购申请单数据" sheetId="1" r:id="rId1"/>
@@ -101,7 +101,7 @@
     <t>{.approveStatusName}</t>
   </si>
   <si>
-    <t>{.isFirstMassProductStr}</t>
+    <t>{.firstMassProductName}</t>
   </si>
   <si>
     <t>{.createPoTypeName}</t>
@@ -1357,6 +1357,7 @@
   <cols>
     <col min="2" max="2" width="11.125" customWidth="1"/>
     <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" spans="1:21">

--- a/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseApplication.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/purchaseApplication.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>申请单号</t>
   </si>
@@ -50,9 +50,6 @@
     <t>产品名称</t>
   </si>
   <si>
-    <t>供应商名称</t>
-  </si>
-  <si>
     <t>计划交期</t>
   </si>
   <si>
@@ -111,9 +108,6 @@
   </si>
   <si>
     <t>{.productName}</t>
-  </si>
-  <si>
-    <t>{.supplierName}</t>
   </si>
   <si>
     <t>{.planDeliveryDate}</t>
@@ -1352,7 +1346,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="11.125" customWidth="1"/>
@@ -1360,7 +1354,7 @@
     <col min="4" max="4" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45" spans="1:21">
+    <row r="1" ht="45" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1421,73 +1415,67 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:20">
+      <c r="A2" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
